--- a/Result/profitability/2477.xlsx
+++ b/Result/profitability/2477.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3524999999999999</v>
+        <v>0.2687499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>24.7425</v>
+        <v>23.62625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2349999999999999</v>
+        <v>0.2262499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>21.9075</v>
+        <v>21.08625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2062499999999999</v>
+        <v>0.1924999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>20.20125</v>
+        <v>19.87</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1874999999999999</v>
+        <v>0.0949999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>18.7175</v>
+        <v>17.92125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0587499999999999</v>
+        <v>-0.0100000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>16.155</v>
+        <v>15.2525</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0425000000000001</v>
+        <v>-0.0475000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>13.735</v>
+        <v>13.70125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0337500000000001</v>
+        <v>-0.0400000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>13.02375</v>
+        <v>12.3475</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.01</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01875000000000009</v>
+        <v>-0.0187500000000001</v>
       </c>
       <c r="N10" t="n">
         <v>12.5675</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2477</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>578</v>
+      </c>
+      <c r="D75" t="n">
+        <v>455</v>
+      </c>
+      <c r="E75" t="n">
+        <v>123</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3387499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.8875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4545454545454546</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2032306536438768</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.925</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.369999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2309644670050761</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
